--- a/docentes/González Sánchez Rene Aurelio - Estadisticos 20222.xlsx
+++ b/docentes/González Sánchez Rene Aurelio - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="46">
   <si>
     <t>Mat</t>
   </si>
@@ -103,6 +103,12 @@
     <t>BONILLA</t>
   </si>
   <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>VENEGAS</t>
+  </si>
+  <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
@@ -121,6 +127,12 @@
     <t>TEXOCO</t>
   </si>
   <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>AMECA</t>
+  </si>
+  <si>
     <t>EDUARDO EMER</t>
   </si>
   <si>
@@ -137,6 +149,12 @@
   </si>
   <si>
     <t>ANGEL ALDAIR</t>
+  </si>
+  <si>
+    <t>SINAI ANTONIO</t>
+  </si>
+  <si>
+    <t>EZEQUIEL</t>
   </si>
 </sst>
 </file>
@@ -1061,7 +1079,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1099,10 +1117,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1122,10 +1140,10 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1145,10 +1163,10 @@
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1168,10 +1186,10 @@
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1191,10 +1209,10 @@
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -1214,10 +1232,10 @@
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -1226,6 +1244,52 @@
         <v>13</v>
       </c>
       <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>21330051920207</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>21330051920287</v>
+      </c>
+      <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Sánchez Rene Aurelio - Estadisticos 20222.xlsx
+++ b/docentes/González Sánchez Rene Aurelio - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="59">
   <si>
     <t>Mat</t>
   </si>
@@ -85,76 +85,115 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>VALENCIA</t>
+  </si>
+  <si>
+    <t>VELASCO</t>
+  </si>
+  <si>
+    <t>ARGÜELLO</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>BONILLA</t>
+  </si>
+  <si>
     <t>BAEZ</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
-    <t>BONILLA</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
+    <t>COCOTLE</t>
   </si>
   <si>
     <t>VENEGAS</t>
   </si>
   <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
+    <t>ANGUIANO</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>SAN JUAN</t>
+  </si>
+  <si>
+    <t>NARANJO</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>ANGUIANO</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
+    <t>CUAQUEHUA</t>
   </si>
   <si>
     <t>AMECA</t>
   </si>
   <si>
+    <t>LLUVIA RUBI</t>
+  </si>
+  <si>
+    <t>TONALLI</t>
+  </si>
+  <si>
+    <t>JULIO</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>FRIDA SOFIA</t>
+  </si>
+  <si>
+    <t>DULCE REGINA</t>
+  </si>
+  <si>
+    <t>ATZIN HEFZIBA</t>
+  </si>
+  <si>
+    <t>LIZBETH</t>
+  </si>
+  <si>
+    <t>ANGEL ALDAIR</t>
+  </si>
+  <si>
     <t>EDUARDO EMER</t>
   </si>
   <si>
-    <t>GUSTAVO</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>FRIDA SOFIA</t>
-  </si>
-  <si>
-    <t>ANGELINA</t>
-  </si>
-  <si>
-    <t>ANGEL ALDAIR</t>
-  </si>
-  <si>
-    <t>SINAI ANTONIO</t>
+    <t>MELANIE</t>
   </si>
   <si>
     <t>EZEQUIEL</t>
+  </si>
+  <si>
+    <t>PEDRO EVER</t>
   </si>
 </sst>
 </file>
@@ -750,16 +789,19 @@
         <v>39</v>
       </c>
       <c r="D2">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>56.41</v>
+      </c>
+      <c r="H2">
+        <v>6.2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -773,16 +815,19 @@
         <v>41</v>
       </c>
       <c r="D3">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>87.8</v>
+      </c>
+      <c r="H3">
+        <v>6.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -796,16 +841,19 @@
         <v>38</v>
       </c>
       <c r="D4">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>81.58</v>
+      </c>
+      <c r="H4">
+        <v>6.3</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -819,16 +867,19 @@
         <v>28</v>
       </c>
       <c r="D5">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>60.71</v>
+      </c>
+      <c r="H5">
+        <v>6.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -930,13 +981,13 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F2">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G2">
-        <v>74.36</v>
+        <v>56.41</v>
       </c>
       <c r="H2">
         <v>6.5</v>
@@ -956,16 +1007,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G3">
-        <v>90.23999999999999</v>
+        <v>87.8</v>
       </c>
       <c r="H3">
-        <v>6.8</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -991,7 +1042,7 @@
         <v>81.58</v>
       </c>
       <c r="H4">
-        <v>6.7</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1008,16 +1059,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F5">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G5">
-        <v>78.56999999999999</v>
+        <v>60.71</v>
       </c>
       <c r="H5">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1079,7 +1130,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1111,16 +1162,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920150</v>
+        <v>22330051920163</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1134,16 +1185,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920386</v>
+        <v>22330051920299</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1157,16 +1208,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920172</v>
+        <v>22330051920170</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1180,16 +1231,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920175</v>
+        <v>22330051920172</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1203,22 +1254,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920088</v>
+        <v>22330051920175</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1226,22 +1277,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920189</v>
+        <v>22330051920287</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1249,22 +1300,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920207</v>
+        <v>21330051920253</v>
       </c>
       <c r="B8" t="s">
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D8" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1272,16 +1323,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920287</v>
+        <v>21330051920257</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D9" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -1290,6 +1341,121 @@
         <v>11</v>
       </c>
       <c r="G9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>21330051920189</v>
+      </c>
+      <c r="B10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>22330051920150</v>
+      </c>
+      <c r="B11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" t="s">
+        <v>55</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>22330051920158</v>
+      </c>
+      <c r="B12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" t="s">
+        <v>56</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>21330051920287</v>
+      </c>
+      <c r="B13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" t="s">
+        <v>57</v>
+      </c>
+      <c r="E13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>21330051920186</v>
+      </c>
+      <c r="B14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Sánchez Rene Aurelio - Estadisticos 20222.xlsx
+++ b/docentes/González Sánchez Rene Aurelio - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="66">
   <si>
     <t>Mat</t>
   </si>
@@ -109,6 +109,9 @@
     <t>FLORES</t>
   </si>
   <si>
+    <t>ROMANOS</t>
+  </si>
+  <si>
     <t>BONILLA</t>
   </si>
   <si>
@@ -145,6 +148,15 @@
     <t>MENDOZA</t>
   </si>
   <si>
+    <t>CELESTINO</t>
+  </si>
+  <si>
+    <t>ESTRADA</t>
+  </si>
+  <si>
+    <t>TEZOCO</t>
+  </si>
+  <si>
     <t>TEXOCO</t>
   </si>
   <si>
@@ -179,6 +191,15 @@
   </si>
   <si>
     <t>LIZBETH</t>
+  </si>
+  <si>
+    <t>KARLA JIMENA</t>
+  </si>
+  <si>
+    <t>GIOVANI</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
   </si>
   <si>
     <t>ANGEL ALDAIR</t>
@@ -724,16 +745,16 @@
         <v>30</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>1</v>
       </c>
       <c r="F7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G7">
-        <v>93.33</v>
+        <v>96.67</v>
       </c>
       <c r="H7">
         <v>6.1</v>
@@ -916,16 +937,19 @@
         <v>30</v>
       </c>
       <c r="D7">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>66.67</v>
+      </c>
+      <c r="H7">
+        <v>6.1</v>
       </c>
     </row>
   </sheetData>
@@ -1108,19 +1132,19 @@
         <v>30</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F7">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="G7">
-        <v>93.33</v>
+        <v>66.67</v>
       </c>
       <c r="H7">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
     </row>
   </sheetData>
@@ -1130,7 +1154,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1171,7 +1195,7 @@
         <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1191,10 +1215,10 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1214,10 +1238,10 @@
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1237,10 +1261,10 @@
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1260,10 +1284,10 @@
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1283,10 +1307,10 @@
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1306,10 +1330,10 @@
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D8" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -1329,10 +1353,10 @@
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -1346,22 +1370,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920189</v>
+        <v>21330051920390</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D10" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1369,93 +1393,162 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920150</v>
+        <v>21330051920041</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920158</v>
+        <v>21330051920059</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D12" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920287</v>
+        <v>21330051920189</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
+        <v>22330051920150</v>
+      </c>
+      <c r="B14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" t="s">
+        <v>62</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>22330051920158</v>
+      </c>
+      <c r="B15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" t="s">
+        <v>63</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>21330051920287</v>
+      </c>
+      <c r="B16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" t="s">
+        <v>64</v>
+      </c>
+      <c r="E16" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
         <v>21330051920186</v>
       </c>
-      <c r="B14" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="B17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" t="s">
         <v>23</v>
       </c>
-      <c r="D14" t="s">
-        <v>58</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
+      <c r="D17" t="s">
+        <v>65</v>
+      </c>
+      <c r="E17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" t="s">
         <v>13</v>
       </c>
-      <c r="G14">
+      <c r="G17">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Sánchez Rene Aurelio - Estadisticos 20222.xlsx
+++ b/docentes/González Sánchez Rene Aurelio - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="77">
   <si>
     <t>Mat</t>
   </si>
@@ -103,6 +103,12 @@
     <t>VELASCO</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
     <t>ARGÜELLO</t>
   </si>
   <si>
@@ -121,6 +127,12 @@
     <t>COCOTLE</t>
   </si>
   <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
     <t>VENEGAS</t>
   </si>
   <si>
@@ -142,6 +154,9 @@
     <t>SAN JUAN</t>
   </si>
   <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
     <t>NARANJO</t>
   </si>
   <si>
@@ -160,12 +175,15 @@
     <t>TEXOCO</t>
   </si>
   <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
     <t>CUAQUEHUA</t>
   </si>
   <si>
+    <t>NAZARIO</t>
+  </si>
+  <si>
+    <t>GALLARDO</t>
+  </si>
+  <si>
     <t>AMECA</t>
   </si>
   <si>
@@ -187,6 +205,15 @@
     <t>DULCE REGINA</t>
   </si>
   <si>
+    <t>DULIAM</t>
+  </si>
+  <si>
+    <t>ARIEL</t>
+  </si>
+  <si>
+    <t>OMAR</t>
+  </si>
+  <si>
     <t>ATZIN HEFZIBA</t>
   </si>
   <si>
@@ -209,6 +236,12 @@
   </si>
   <si>
     <t>MELANIE</t>
+  </si>
+  <si>
+    <t>EDGAR</t>
+  </si>
+  <si>
+    <t>CARLOS</t>
   </si>
   <si>
     <t>EZEQUIEL</t>
@@ -914,16 +947,19 @@
         <v>32</v>
       </c>
       <c r="D6">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>56.25</v>
+      </c>
+      <c r="H6">
+        <v>6.3</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1109,16 +1145,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F6">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="G6">
-        <v>100</v>
+        <v>56.25</v>
       </c>
       <c r="H6">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1154,7 +1190,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1195,7 +1231,7 @@
         <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1215,10 +1251,10 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1238,10 +1274,10 @@
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1261,10 +1297,10 @@
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1284,10 +1320,10 @@
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1307,10 +1343,10 @@
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D7" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1324,22 +1360,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920253</v>
+        <v>20330051920078</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="D8" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1347,22 +1383,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920257</v>
+        <v>21330051920012</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1370,22 +1406,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920390</v>
+        <v>21330051920013</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1393,22 +1429,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920041</v>
+        <v>21330051920253</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1416,22 +1452,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920059</v>
+        <v>21330051920257</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D12" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1439,22 +1475,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920189</v>
+        <v>21330051920390</v>
       </c>
       <c r="B13" t="s">
         <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D13" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -1462,93 +1498,208 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920150</v>
+        <v>21330051920041</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D14" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="E14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920158</v>
+        <v>21330051920059</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C15" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D15" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="E15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G15">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920287</v>
+        <v>21330051920189</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C16" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D16" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G16">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
+        <v>22330051920150</v>
+      </c>
+      <c r="B17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" t="s">
+        <v>45</v>
+      </c>
+      <c r="D17" t="s">
+        <v>71</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>22330051920158</v>
+      </c>
+      <c r="B18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" t="s">
+        <v>52</v>
+      </c>
+      <c r="D18" t="s">
+        <v>72</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>20330051920018</v>
+      </c>
+      <c r="B19" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" t="s">
+        <v>73</v>
+      </c>
+      <c r="E19" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>21330051920018</v>
+      </c>
+      <c r="B20" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" t="s">
+        <v>74</v>
+      </c>
+      <c r="E20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" t="s">
+        <v>14</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>21330051920287</v>
+      </c>
+      <c r="B21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" t="s">
+        <v>55</v>
+      </c>
+      <c r="D21" t="s">
+        <v>75</v>
+      </c>
+      <c r="E21" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" t="s">
+        <v>11</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
         <v>21330051920186</v>
       </c>
-      <c r="B17" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="B22" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" t="s">
         <v>23</v>
       </c>
-      <c r="D17" t="s">
-        <v>65</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" t="s">
+      <c r="D22" t="s">
+        <v>76</v>
+      </c>
+      <c r="E22" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" t="s">
         <v>13</v>
       </c>
-      <c r="G17">
+      <c r="G22">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Sánchez Rene Aurelio - Estadisticos 20222.xlsx
+++ b/docentes/González Sánchez Rene Aurelio - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="31">
   <si>
     <t>Mat</t>
   </si>
@@ -85,169 +85,31 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
     <t>CRUZ</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>VELASCO</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>ARGÜELLO</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>ROMANOS</t>
-  </si>
-  <si>
-    <t>BONILLA</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>VENEGAS</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
-    <t>ANGUIANO</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>SAN JUAN</t>
+    <t>ESTRADA</t>
   </si>
   <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
-    <t>NARANJO</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>CELESTINO</t>
-  </si>
-  <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>CUAQUEHUA</t>
-  </si>
-  <si>
-    <t>NAZARIO</t>
-  </si>
-  <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
-    <t>AMECA</t>
-  </si>
-  <si>
-    <t>LLUVIA RUBI</t>
-  </si>
-  <si>
-    <t>TONALLI</t>
-  </si>
-  <si>
-    <t>JULIO</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>FRIDA SOFIA</t>
-  </si>
-  <si>
-    <t>DULCE REGINA</t>
-  </si>
-  <si>
-    <t>DULIAM</t>
-  </si>
-  <si>
-    <t>ARIEL</t>
-  </si>
-  <si>
-    <t>OMAR</t>
-  </si>
-  <si>
-    <t>ATZIN HEFZIBA</t>
-  </si>
-  <si>
-    <t>LIZBETH</t>
-  </si>
-  <si>
-    <t>KARLA JIMENA</t>
+    <t>LIZBETH JOSELYN</t>
   </si>
   <si>
     <t>GIOVANI</t>
   </si>
   <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
-    <t>ANGEL ALDAIR</t>
-  </si>
-  <si>
     <t>EDUARDO EMER</t>
-  </si>
-  <si>
-    <t>MELANIE</t>
-  </si>
-  <si>
-    <t>EDGAR</t>
-  </si>
-  <si>
-    <t>CARLOS</t>
-  </si>
-  <si>
-    <t>EZEQUIEL</t>
-  </si>
-  <si>
-    <t>PEDRO EVER</t>
   </si>
 </sst>
 </file>
@@ -1041,16 +903,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="G2">
-        <v>56.41</v>
+        <v>84.62</v>
       </c>
       <c r="H2">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1067,16 +929,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G3">
-        <v>87.8</v>
+        <v>95.12</v>
       </c>
       <c r="H3">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1119,16 +981,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="G5">
-        <v>60.71</v>
+        <v>92.86</v>
       </c>
       <c r="H5">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1145,16 +1007,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="G6">
-        <v>56.25</v>
+        <v>93.75</v>
       </c>
       <c r="H6">
-        <v>6.2</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1171,16 +1033,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F7">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G7">
-        <v>66.67</v>
+        <v>83.33</v>
       </c>
       <c r="H7">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
@@ -1190,7 +1052,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1222,22 +1084,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920163</v>
+        <v>21330051920235</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1245,22 +1107,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920299</v>
+        <v>21330051920041</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1268,16 +1130,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920170</v>
+        <v>22330051920150</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1286,420 +1148,6 @@
         <v>10</v>
       </c>
       <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>22330051920172</v>
-      </c>
-      <c r="B5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>22330051920175</v>
-      </c>
-      <c r="B6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" t="s">
-        <v>43</v>
-      </c>
-      <c r="D6" t="s">
-        <v>60</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>22330051920287</v>
-      </c>
-      <c r="B7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" t="s">
-        <v>44</v>
-      </c>
-      <c r="D7" t="s">
-        <v>61</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>20330051920078</v>
-      </c>
-      <c r="B8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" t="s">
-        <v>62</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920012</v>
-      </c>
-      <c r="B9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" t="s">
-        <v>63</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920013</v>
-      </c>
-      <c r="B10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D10" t="s">
-        <v>64</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051920253</v>
-      </c>
-      <c r="B11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" t="s">
-        <v>46</v>
-      </c>
-      <c r="D11" t="s">
-        <v>65</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>11</v>
-      </c>
-      <c r="G11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920257</v>
-      </c>
-      <c r="B12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" t="s">
-        <v>47</v>
-      </c>
-      <c r="D12" t="s">
-        <v>66</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920390</v>
-      </c>
-      <c r="B13" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" t="s">
-        <v>48</v>
-      </c>
-      <c r="D13" t="s">
-        <v>67</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>15</v>
-      </c>
-      <c r="G13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920041</v>
-      </c>
-      <c r="B14" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14" t="s">
-        <v>49</v>
-      </c>
-      <c r="D14" t="s">
-        <v>68</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
-        <v>15</v>
-      </c>
-      <c r="G14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920059</v>
-      </c>
-      <c r="B15" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" t="s">
-        <v>50</v>
-      </c>
-      <c r="D15" t="s">
-        <v>69</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>21330051920189</v>
-      </c>
-      <c r="B16" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16" t="s">
-        <v>51</v>
-      </c>
-      <c r="D16" t="s">
-        <v>70</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" t="s">
-        <v>13</v>
-      </c>
-      <c r="G16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>22330051920150</v>
-      </c>
-      <c r="B17" t="s">
-        <v>34</v>
-      </c>
-      <c r="C17" t="s">
-        <v>45</v>
-      </c>
-      <c r="D17" t="s">
-        <v>71</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>10</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>22330051920158</v>
-      </c>
-      <c r="B18" t="s">
-        <v>35</v>
-      </c>
-      <c r="C18" t="s">
-        <v>52</v>
-      </c>
-      <c r="D18" t="s">
-        <v>72</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>10</v>
-      </c>
-      <c r="G18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>20330051920018</v>
-      </c>
-      <c r="B19" t="s">
-        <v>36</v>
-      </c>
-      <c r="C19" t="s">
-        <v>53</v>
-      </c>
-      <c r="D19" t="s">
-        <v>73</v>
-      </c>
-      <c r="E19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" t="s">
-        <v>14</v>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>21330051920018</v>
-      </c>
-      <c r="B20" t="s">
-        <v>37</v>
-      </c>
-      <c r="C20" t="s">
-        <v>54</v>
-      </c>
-      <c r="D20" t="s">
-        <v>74</v>
-      </c>
-      <c r="E20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" t="s">
-        <v>14</v>
-      </c>
-      <c r="G20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>21330051920287</v>
-      </c>
-      <c r="B21" t="s">
-        <v>38</v>
-      </c>
-      <c r="C21" t="s">
-        <v>55</v>
-      </c>
-      <c r="D21" t="s">
-        <v>75</v>
-      </c>
-      <c r="E21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" t="s">
-        <v>11</v>
-      </c>
-      <c r="G21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>21330051920186</v>
-      </c>
-      <c r="B22" t="s">
-        <v>39</v>
-      </c>
-      <c r="C22" t="s">
-        <v>23</v>
-      </c>
-      <c r="D22" t="s">
-        <v>76</v>
-      </c>
-      <c r="E22" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" t="s">
-        <v>13</v>
-      </c>
-      <c r="G22">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Sánchez Rene Aurelio - Estadisticos 20222.xlsx
+++ b/docentes/González Sánchez Rene Aurelio - Estadisticos 20222.xlsx
@@ -88,7 +88,7 @@
     <t>IXMATLAHUA</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
+    <t>ZEPEDA</t>
   </si>
   <si>
     <t>BAEZ</t>
@@ -97,7 +97,7 @@
     <t>CRUZ</t>
   </si>
   <si>
-    <t>ESTRADA</t>
+    <t>MORALES</t>
   </si>
   <si>
     <t>DE LA CRUZ</t>
@@ -106,7 +106,7 @@
     <t>LIZBETH JOSELYN</t>
   </si>
   <si>
-    <t>GIOVANI</t>
+    <t>YAEL</t>
   </si>
   <si>
     <t>EDUARDO EMER</t>
@@ -1107,7 +1107,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920041</v>
+        <v>21330051920222</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
@@ -1122,7 +1122,7 @@
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G3">
         <v>2</v>

--- a/docentes/González Sánchez Rene Aurelio - Estadisticos 20222.xlsx
+++ b/docentes/González Sánchez Rene Aurelio - Estadisticos 20222.xlsx
@@ -85,7 +85,7 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>IXMATLAHUA</t>
+    <t>RAMIREZ</t>
   </si>
   <si>
     <t>ZEPEDA</t>
@@ -94,7 +94,7 @@
     <t>BAEZ</t>
   </si>
   <si>
-    <t>CRUZ</t>
+    <t>LUNA</t>
   </si>
   <si>
     <t>MORALES</t>
@@ -103,7 +103,7 @@
     <t>DE LA CRUZ</t>
   </si>
   <si>
-    <t>LIZBETH JOSELYN</t>
+    <t>GUSTAVO</t>
   </si>
   <si>
     <t>YAEL</t>
@@ -1084,7 +1084,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920235</v>
+        <v>22330051920386</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
@@ -1096,10 +1096,10 @@
         <v>28</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>2</v>
